--- a/docs/data/presentation/MAT111.xlsx
+++ b/docs/data/presentation/MAT111.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\erenimo\projects\ses\docs\data\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F51378-647E-4F53-980D-D38615EFE0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1748A35-338E-4F95-AD76-2D068ED46146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="448">
   <si>
     <t>No_0833AB</t>
   </si>
@@ -183,9 +183,6 @@
   </si>
   <si>
     <t>studentsurname20</t>
-  </si>
-  <si>
-    <t>261401001</t>
   </si>
   <si>
     <t>261401002</t>
@@ -1389,7 +1386,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1408,6 +1405,13 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1459,7 +1463,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -1483,6 +1487,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2665,16 +2672,16 @@
         <v>4</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>5</v>
@@ -2684,8 +2691,8 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>50</v>
+      <c r="B2" s="8">
+        <v>261401001</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>11</v>
@@ -2710,17 +2717,14 @@
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="7">
-        <f>G2 * 0.2 + H2 * 0.2 + I2 * 0.2 + J2 * 0.4</f>
-        <v>15.600000000000001</v>
-      </c>
+      <c r="L2" s="7"/>
     </row>
     <row r="3" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
@@ -2745,17 +2749,14 @@
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="7">
-        <f t="shared" ref="L3:L66" si="0">G3 * 0.2 + H3 * 0.2 + I3 * 0.2 + J3 * 0.4</f>
-        <v>0</v>
-      </c>
+      <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -2782,17 +2783,14 @@
         <v>67.058823529411768</v>
       </c>
       <c r="K4" s="3"/>
-      <c r="L4" s="7">
-        <f t="shared" si="0"/>
-        <v>76.623529411764707</v>
-      </c>
+      <c r="L4" s="7"/>
     </row>
     <row r="5" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>16</v>
@@ -2819,17 +2817,14 @@
         <v>36.666666666666671</v>
       </c>
       <c r="K5" s="3"/>
-      <c r="L5" s="7">
-        <f t="shared" si="0"/>
-        <v>44.266666666666673</v>
-      </c>
+      <c r="L5" s="7"/>
     </row>
     <row r="6" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>18</v>
@@ -2856,17 +2851,14 @@
         <v>60</v>
       </c>
       <c r="K6" s="3"/>
-      <c r="L6" s="7">
-        <f t="shared" si="0"/>
-        <v>46.8</v>
-      </c>
+      <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
@@ -2893,17 +2885,14 @@
         <v>55.294117647058826</v>
       </c>
       <c r="K7" s="3"/>
-      <c r="L7" s="7">
-        <f t="shared" si="0"/>
-        <v>52.517647058823528</v>
-      </c>
+      <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>22</v>
@@ -2930,17 +2919,14 @@
         <v>45.882352941176471</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="7">
-        <f t="shared" si="0"/>
-        <v>54.7529411764706</v>
-      </c>
+      <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>24</v>
@@ -2967,17 +2953,14 @@
         <v>58.888888888888893</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="7">
-        <f t="shared" si="0"/>
-        <v>51.555555555555557</v>
-      </c>
+      <c r="L9" s="7"/>
     </row>
     <row r="10" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>26</v>
@@ -3004,17 +2987,14 @@
         <v>69.411764705882362</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="7">
-        <f t="shared" si="0"/>
-        <v>70.964705882352945</v>
-      </c>
+      <c r="L10" s="7"/>
     </row>
     <row r="11" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>28</v>
@@ -3041,17 +3021,14 @@
         <v>81.17647058823529</v>
       </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="7">
-        <f t="shared" si="0"/>
-        <v>89.470588235294116</v>
-      </c>
+      <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>30</v>
@@ -3078,17 +3055,14 @@
         <v>17.647058823529413</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="7">
-        <f t="shared" si="0"/>
-        <v>19.258823529411767</v>
-      </c>
+      <c r="L12" s="7"/>
     </row>
     <row r="13" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
@@ -3115,17 +3089,14 @@
         <v>25.555555555555557</v>
       </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="7">
-        <f t="shared" si="0"/>
-        <v>29.422222222222224</v>
-      </c>
+      <c r="L13" s="7"/>
     </row>
     <row r="14" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>34</v>
@@ -3152,17 +3123,14 @@
         <v>15.555555555555557</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="7">
-        <f t="shared" si="0"/>
-        <v>38.022222222222219</v>
-      </c>
+      <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>36</v>
@@ -3189,17 +3157,14 @@
         <v>72.222222222222229</v>
       </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="7">
-        <f t="shared" si="0"/>
-        <v>50.888888888888893</v>
-      </c>
+      <c r="L15" s="7"/>
     </row>
     <row r="16" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>38</v>
@@ -3224,17 +3189,14 @@
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="L16" s="7"/>
     </row>
     <row r="17" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>40</v>
@@ -3261,17 +3223,14 @@
         <v>61.176470588235297</v>
       </c>
       <c r="K17" s="3"/>
-      <c r="L17" s="7">
-        <f t="shared" si="0"/>
-        <v>63.070588235294125</v>
-      </c>
+      <c r="L17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>42</v>
@@ -3298,17 +3257,14 @@
         <v>64.444444444444443</v>
       </c>
       <c r="K18" s="3"/>
-      <c r="L18" s="7">
-        <f t="shared" si="0"/>
-        <v>45.977777777777781</v>
-      </c>
+      <c r="L18" s="7"/>
     </row>
     <row r="19" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>44</v>
@@ -3335,17 +3291,14 @@
         <v>96.666666666666671</v>
       </c>
       <c r="K19" s="3"/>
-      <c r="L19" s="7">
-        <f t="shared" si="0"/>
-        <v>73.466666666666669</v>
-      </c>
+      <c r="L19" s="7"/>
     </row>
     <row r="20" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>46</v>
@@ -3372,17 +3325,14 @@
         <v>46.666666666666671</v>
       </c>
       <c r="K20" s="3"/>
-      <c r="L20" s="7">
-        <f t="shared" si="0"/>
-        <v>49.466666666666669</v>
-      </c>
+      <c r="L20" s="7"/>
     </row>
     <row r="21" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>48</v>
@@ -3409,23 +3359,20 @@
         <v>64.444444444444443</v>
       </c>
       <c r="K21" s="3"/>
-      <c r="L21" s="7">
-        <f t="shared" si="0"/>
-        <v>55.977777777777781</v>
-      </c>
+      <c r="L21" s="7"/>
     </row>
     <row r="22" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -3440,23 +3387,20 @@
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="L22" s="7"/>
     </row>
     <row r="23" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -3471,23 +3415,20 @@
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="3"/>
-      <c r="L23" s="7">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
-      </c>
+      <c r="L23" s="7"/>
     </row>
     <row r="24" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -3504,23 +3445,20 @@
         <v>85.882352941176478</v>
       </c>
       <c r="K24" s="3"/>
-      <c r="L24" s="7">
-        <f t="shared" si="0"/>
-        <v>80.472941176470584</v>
-      </c>
+      <c r="L24" s="7"/>
     </row>
     <row r="25" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -3537,23 +3475,20 @@
         <v>100</v>
       </c>
       <c r="K25" s="3"/>
-      <c r="L25" s="7">
-        <f t="shared" si="0"/>
-        <v>97.8</v>
-      </c>
+      <c r="L25" s="7"/>
     </row>
     <row r="26" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -3570,23 +3505,20 @@
         <v>98.8888888888889</v>
       </c>
       <c r="K26" s="3"/>
-      <c r="L26" s="7">
-        <f t="shared" si="0"/>
-        <v>97.795555555555552</v>
-      </c>
+      <c r="L26" s="7"/>
     </row>
     <row r="27" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -3603,23 +3535,20 @@
         <v>87.058823529411768</v>
       </c>
       <c r="K27" s="3"/>
-      <c r="L27" s="7">
-        <f t="shared" si="0"/>
-        <v>70.063529411764705</v>
-      </c>
+      <c r="L27" s="7"/>
     </row>
     <row r="28" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -3636,23 +3565,20 @@
         <v>100</v>
       </c>
       <c r="K28" s="3"/>
-      <c r="L28" s="7">
-        <f t="shared" si="0"/>
-        <v>97.36</v>
-      </c>
+      <c r="L28" s="7"/>
     </row>
     <row r="29" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -3669,23 +3595,20 @@
         <v>29.411764705882355</v>
       </c>
       <c r="K29" s="3"/>
-      <c r="L29" s="7">
-        <f t="shared" si="0"/>
-        <v>50.004705882352944</v>
-      </c>
+      <c r="L29" s="7"/>
     </row>
     <row r="30" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -3702,23 +3625,20 @@
         <v>100</v>
       </c>
       <c r="K30" s="3"/>
-      <c r="L30" s="7">
-        <f t="shared" si="0"/>
-        <v>98.52</v>
-      </c>
+      <c r="L30" s="7"/>
     </row>
     <row r="31" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -3735,23 +3655,20 @@
         <v>100</v>
       </c>
       <c r="K31" s="3"/>
-      <c r="L31" s="7">
-        <f t="shared" si="0"/>
-        <v>97.32</v>
-      </c>
+      <c r="L31" s="7"/>
     </row>
     <row r="32" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -3768,23 +3685,20 @@
         <v>105.88235294117648</v>
       </c>
       <c r="K32" s="3"/>
-      <c r="L32" s="7">
-        <f t="shared" si="0"/>
-        <v>95.952941176470603</v>
-      </c>
+      <c r="L32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -3801,23 +3715,20 @@
         <v>48.235294117647058</v>
       </c>
       <c r="K33" s="3"/>
-      <c r="L33" s="7">
-        <f t="shared" si="0"/>
-        <v>65.094117647058823</v>
-      </c>
+      <c r="L33" s="7"/>
     </row>
     <row r="34" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -3834,23 +3745,20 @@
         <v>90.588235294117652</v>
       </c>
       <c r="K34" s="3"/>
-      <c r="L34" s="7">
-        <f t="shared" si="0"/>
-        <v>95.395294117647069</v>
-      </c>
+      <c r="L34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -3867,23 +3775,20 @@
         <v>83.529411764705884</v>
       </c>
       <c r="K35" s="3"/>
-      <c r="L35" s="7">
-        <f t="shared" si="0"/>
-        <v>92.931764705882358</v>
-      </c>
+      <c r="L35" s="7"/>
     </row>
     <row r="36" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -3900,23 +3805,20 @@
         <v>91.764705882352942</v>
       </c>
       <c r="K36" s="3"/>
-      <c r="L36" s="7">
-        <f t="shared" si="0"/>
-        <v>94.22588235294117</v>
-      </c>
+      <c r="L36" s="7"/>
     </row>
     <row r="37" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -3933,23 +3835,20 @@
         <v>98.82352941176471</v>
       </c>
       <c r="K37" s="3"/>
-      <c r="L37" s="7">
-        <f t="shared" si="0"/>
-        <v>93.209411764705891</v>
-      </c>
+      <c r="L37" s="7"/>
     </row>
     <row r="38" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -3966,23 +3865,20 @@
         <v>92.941176470588232</v>
       </c>
       <c r="K38" s="3"/>
-      <c r="L38" s="7">
-        <f t="shared" si="0"/>
-        <v>93.496470588235297</v>
-      </c>
+      <c r="L38" s="7"/>
     </row>
     <row r="39" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -3999,23 +3895,20 @@
         <v>84.705882352941174</v>
       </c>
       <c r="K39" s="3"/>
-      <c r="L39" s="7">
-        <f t="shared" si="0"/>
-        <v>71.642352941176483</v>
-      </c>
+      <c r="L39" s="7"/>
     </row>
     <row r="40" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -4032,23 +3925,20 @@
         <v>47.058823529411768</v>
       </c>
       <c r="K40" s="3"/>
-      <c r="L40" s="7">
-        <f t="shared" si="0"/>
-        <v>50.82352941176471</v>
-      </c>
+      <c r="L40" s="7"/>
     </row>
     <row r="41" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -4065,23 +3955,20 @@
         <v>4.7058823529411766</v>
       </c>
       <c r="K41" s="3"/>
-      <c r="L41" s="7">
-        <f t="shared" si="0"/>
-        <v>10.482352941176472</v>
-      </c>
+      <c r="L41" s="7"/>
     </row>
     <row r="42" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -4098,23 +3985,20 @@
         <v>42.352941176470587</v>
       </c>
       <c r="K42" s="3"/>
-      <c r="L42" s="7">
-        <f t="shared" si="0"/>
-        <v>56.221176470588233</v>
-      </c>
+      <c r="L42" s="7"/>
     </row>
     <row r="43" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -4131,23 +4015,20 @@
         <v>100</v>
       </c>
       <c r="K43" s="3"/>
-      <c r="L43" s="7">
-        <f t="shared" si="0"/>
-        <v>95.68</v>
-      </c>
+      <c r="L43" s="7"/>
     </row>
     <row r="44" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -4164,23 +4045,20 @@
         <v>4.7058823529411766</v>
       </c>
       <c r="K44" s="3"/>
-      <c r="L44" s="7">
-        <f t="shared" si="0"/>
-        <v>16.162352941176472</v>
-      </c>
+      <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -4197,23 +4075,20 @@
         <v>43.333333333333336</v>
       </c>
       <c r="K45" s="3"/>
-      <c r="L45" s="7">
-        <f t="shared" si="0"/>
-        <v>41.613333333333337</v>
-      </c>
+      <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -4230,23 +4105,20 @@
         <v>78.888888888888886</v>
       </c>
       <c r="K46" s="3"/>
-      <c r="L46" s="7">
-        <f t="shared" si="0"/>
-        <v>61.555555555555557</v>
-      </c>
+      <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -4263,23 +4135,20 @@
         <v>91.111111111111114</v>
       </c>
       <c r="K47" s="3"/>
-      <c r="L47" s="7">
-        <f t="shared" si="0"/>
-        <v>54.844444444444449</v>
-      </c>
+      <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -4296,23 +4165,20 @@
         <v>92.941176470588232</v>
       </c>
       <c r="K48" s="3"/>
-      <c r="L48" s="7">
-        <f t="shared" si="0"/>
-        <v>91.296470588235309</v>
-      </c>
+      <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -4329,23 +4195,20 @@
         <v>100</v>
       </c>
       <c r="K49" s="3"/>
-      <c r="L49" s="7">
-        <f t="shared" si="0"/>
-        <v>99.12</v>
-      </c>
+      <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -4362,23 +4225,20 @@
         <v>81.17647058823529</v>
       </c>
       <c r="K50" s="3"/>
-      <c r="L50" s="7">
-        <f t="shared" si="0"/>
-        <v>72.150588235294123</v>
-      </c>
+      <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -4395,23 +4255,20 @@
         <v>74.117647058823536</v>
       </c>
       <c r="K51" s="3"/>
-      <c r="L51" s="7">
-        <f t="shared" si="0"/>
-        <v>86.087058823529432</v>
-      </c>
+      <c r="L51" s="7"/>
     </row>
     <row r="52" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -4428,23 +4285,20 @@
         <v>89.411764705882362</v>
       </c>
       <c r="K52" s="3"/>
-      <c r="L52" s="7">
-        <f t="shared" si="0"/>
-        <v>88.204705882352954</v>
-      </c>
+      <c r="L52" s="7"/>
     </row>
     <row r="53" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
@@ -4461,23 +4315,20 @@
         <v>75.294117647058826</v>
       </c>
       <c r="K53" s="3"/>
-      <c r="L53" s="7">
-        <f t="shared" si="0"/>
-        <v>72.517647058823542</v>
-      </c>
+      <c r="L53" s="7"/>
     </row>
     <row r="54" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -4494,23 +4345,20 @@
         <v>72.941176470588232</v>
       </c>
       <c r="K54" s="3"/>
-      <c r="L54" s="7">
-        <f t="shared" si="0"/>
-        <v>80.17647058823529</v>
-      </c>
+      <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -4527,23 +4375,20 @@
         <v>70.588235294117652</v>
       </c>
       <c r="K55" s="3"/>
-      <c r="L55" s="7">
-        <f t="shared" si="0"/>
-        <v>81.675294117647056</v>
-      </c>
+      <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -4560,23 +4405,20 @@
         <v>75.294117647058826</v>
       </c>
       <c r="K56" s="3"/>
-      <c r="L56" s="7">
-        <f t="shared" si="0"/>
-        <v>74.95764705882354</v>
-      </c>
+      <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -4591,23 +4433,20 @@
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
-      <c r="L57" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
@@ -4624,23 +4463,20 @@
         <v>47.058823529411768</v>
       </c>
       <c r="K58" s="3"/>
-      <c r="L58" s="7">
-        <f t="shared" si="0"/>
-        <v>63.863529411764716</v>
-      </c>
+      <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
@@ -4657,23 +4493,20 @@
         <v>34.117647058823529</v>
       </c>
       <c r="K59" s="3"/>
-      <c r="L59" s="7">
-        <f t="shared" si="0"/>
-        <v>46.607058823529414</v>
-      </c>
+      <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -4690,23 +4523,20 @@
         <v>100</v>
       </c>
       <c r="K60" s="3"/>
-      <c r="L60" s="7">
-        <f t="shared" si="0"/>
-        <v>98.48</v>
-      </c>
+      <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -4723,23 +4553,20 @@
         <v>100</v>
       </c>
       <c r="K61" s="6"/>
-      <c r="L61" s="7">
-        <f t="shared" si="0"/>
-        <v>94.160000000000011</v>
-      </c>
+      <c r="L61" s="7"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
@@ -4756,23 +4583,20 @@
         <v>100</v>
       </c>
       <c r="K62" s="6"/>
-      <c r="L62" s="7">
-        <f t="shared" si="0"/>
-        <v>96.32</v>
-      </c>
+      <c r="L62" s="7"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -4789,23 +4613,20 @@
         <v>95.294117647058826</v>
       </c>
       <c r="K63" s="6"/>
-      <c r="L63" s="7">
-        <f t="shared" si="0"/>
-        <v>89.397647058823537</v>
-      </c>
+      <c r="L63" s="7"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
@@ -4822,23 +4643,20 @@
         <v>54.117647058823529</v>
       </c>
       <c r="K64" s="6"/>
-      <c r="L64" s="7">
-        <f t="shared" si="0"/>
-        <v>57.887058823529415</v>
-      </c>
+      <c r="L64" s="7"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
@@ -4855,23 +4673,20 @@
         <v>95.294117647058826</v>
       </c>
       <c r="K65" s="6"/>
-      <c r="L65" s="7">
-        <f t="shared" si="0"/>
-        <v>93.557647058823534</v>
-      </c>
+      <c r="L65" s="7"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
@@ -4888,23 +4703,20 @@
         <v>65.882352941176478</v>
       </c>
       <c r="K66" s="6"/>
-      <c r="L66" s="7">
-        <f t="shared" si="0"/>
-        <v>75.912941176470596</v>
-      </c>
+      <c r="L66" s="7"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
@@ -4921,23 +4733,20 @@
         <v>76.470588235294116</v>
       </c>
       <c r="K67" s="6"/>
-      <c r="L67" s="7">
-        <f t="shared" ref="L67:L130" si="1">G67 * 0.2 + H67 * 0.2 + I67 * 0.2 + J67 * 0.4</f>
-        <v>82.828235294117647</v>
-      </c>
+      <c r="L67" s="7"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
@@ -4954,23 +4763,20 @@
         <v>78.82352941176471</v>
       </c>
       <c r="K68" s="6"/>
-      <c r="L68" s="7">
-        <f t="shared" si="1"/>
-        <v>86.849411764705877</v>
-      </c>
+      <c r="L68" s="7"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -4987,23 +4793,20 @@
         <v>50.588235294117652</v>
       </c>
       <c r="K69" s="6"/>
-      <c r="L69" s="7">
-        <f t="shared" si="1"/>
-        <v>57.555294117647065</v>
-      </c>
+      <c r="L69" s="7"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
@@ -5020,23 +4823,20 @@
         <v>92.941176470588232</v>
       </c>
       <c r="K70" s="6"/>
-      <c r="L70" s="7">
-        <f t="shared" si="1"/>
-        <v>96.616470588235302</v>
-      </c>
+      <c r="L70" s="7"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -5053,23 +4853,20 @@
         <v>82.352941176470594</v>
       </c>
       <c r="K71" s="6"/>
-      <c r="L71" s="7">
-        <f t="shared" si="1"/>
-        <v>73.701176470588251</v>
-      </c>
+      <c r="L71" s="7"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
@@ -5086,23 +4883,20 @@
         <v>55.294117647058826</v>
       </c>
       <c r="K72" s="6"/>
-      <c r="L72" s="7">
-        <f t="shared" si="1"/>
-        <v>66.757647058823537</v>
-      </c>
+      <c r="L72" s="7"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
@@ -5119,23 +4913,20 @@
         <v>75.294117647058826</v>
       </c>
       <c r="K73" s="6"/>
-      <c r="L73" s="7">
-        <f t="shared" si="1"/>
-        <v>75.557647058823534</v>
-      </c>
+      <c r="L73" s="7"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
@@ -5152,23 +4943,20 @@
         <v>68.235294117647058</v>
       </c>
       <c r="K74" s="6"/>
-      <c r="L74" s="7">
-        <f t="shared" si="1"/>
-        <v>58.894117647058827</v>
-      </c>
+      <c r="L74" s="7"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -5185,23 +4973,20 @@
         <v>50.588235294117652</v>
       </c>
       <c r="K75" s="6"/>
-      <c r="L75" s="7">
-        <f t="shared" si="1"/>
-        <v>51.15529411764706</v>
-      </c>
+      <c r="L75" s="7"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -5218,23 +5003,20 @@
         <v>27.058823529411764</v>
       </c>
       <c r="K76" s="6"/>
-      <c r="L76" s="7">
-        <f t="shared" si="1"/>
-        <v>33.303529411764714</v>
-      </c>
+      <c r="L76" s="7"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
@@ -5251,23 +5033,20 @@
         <v>61.176470588235297</v>
       </c>
       <c r="K77" s="6"/>
-      <c r="L77" s="7">
-        <f t="shared" si="1"/>
-        <v>56.870588235294122</v>
-      </c>
+      <c r="L77" s="7"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -5284,23 +5063,20 @@
         <v>60</v>
       </c>
       <c r="K78" s="6"/>
-      <c r="L78" s="7">
-        <f t="shared" si="1"/>
-        <v>75.48</v>
-      </c>
+      <c r="L78" s="7"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -5315,23 +5091,20 @@
       </c>
       <c r="J79" s="6"/>
       <c r="K79" s="6"/>
-      <c r="L79" s="7">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
+      <c r="L79" s="7"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -5348,23 +5121,20 @@
         <v>64.705882352941174</v>
       </c>
       <c r="K80" s="6"/>
-      <c r="L80" s="7">
-        <f t="shared" si="1"/>
-        <v>52.042352941176475</v>
-      </c>
+      <c r="L80" s="7"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -5381,23 +5151,20 @@
         <v>83.333333333333343</v>
       </c>
       <c r="K81" s="6"/>
-      <c r="L81" s="7">
-        <f t="shared" si="1"/>
-        <v>59.853333333333339</v>
-      </c>
+      <c r="L81" s="7"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -5414,23 +5181,20 @@
         <v>77.777777777777786</v>
       </c>
       <c r="K82" s="6"/>
-      <c r="L82" s="7">
-        <f t="shared" si="1"/>
-        <v>47.111111111111114</v>
-      </c>
+      <c r="L82" s="7"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -5447,23 +5211,20 @@
         <v>78.82352941176471</v>
       </c>
       <c r="K83" s="6"/>
-      <c r="L83" s="7">
-        <f t="shared" si="1"/>
-        <v>72.849411764705877</v>
-      </c>
+      <c r="L83" s="7"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -5480,23 +5241,20 @@
         <v>23.333333333333336</v>
       </c>
       <c r="K84" s="6"/>
-      <c r="L84" s="7">
-        <f t="shared" si="1"/>
-        <v>32.533333333333339</v>
-      </c>
+      <c r="L84" s="7"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -5513,23 +5271,20 @@
         <v>69.411764705882362</v>
       </c>
       <c r="K85" s="6"/>
-      <c r="L85" s="7">
-        <f t="shared" si="1"/>
-        <v>85.484705882352941</v>
-      </c>
+      <c r="L85" s="7"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
@@ -5546,23 +5301,20 @@
         <v>49.411764705882355</v>
       </c>
       <c r="K86" s="6"/>
-      <c r="L86" s="7">
-        <f t="shared" si="1"/>
-        <v>44.964705882352945</v>
-      </c>
+      <c r="L86" s="7"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
@@ -5579,23 +5331,20 @@
         <v>80</v>
       </c>
       <c r="K87" s="6"/>
-      <c r="L87" s="7">
-        <f t="shared" si="1"/>
-        <v>65.2</v>
-      </c>
+      <c r="L87" s="7"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -5612,23 +5361,20 @@
         <v>72.941176470588232</v>
       </c>
       <c r="K88" s="6"/>
-      <c r="L88" s="7">
-        <f t="shared" si="1"/>
-        <v>63.17647058823529</v>
-      </c>
+      <c r="L88" s="7"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -5645,23 +5391,20 @@
         <v>38.82352941176471</v>
       </c>
       <c r="K89" s="6"/>
-      <c r="L89" s="7">
-        <f t="shared" si="1"/>
-        <v>54.92941176470589</v>
-      </c>
+      <c r="L89" s="7"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -5678,23 +5421,20 @@
         <v>62.352941176470587</v>
       </c>
       <c r="K90" s="6"/>
-      <c r="L90" s="7">
-        <f t="shared" si="1"/>
-        <v>42.141176470588235</v>
-      </c>
+      <c r="L90" s="7"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
@@ -5709,23 +5449,20 @@
       </c>
       <c r="J91" s="6"/>
       <c r="K91" s="6"/>
-      <c r="L91" s="7">
-        <f t="shared" si="1"/>
-        <v>31.28</v>
-      </c>
+      <c r="L91" s="7"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
@@ -5742,23 +5479,20 @@
         <v>70.588235294117652</v>
       </c>
       <c r="K92" s="6"/>
-      <c r="L92" s="7">
-        <f t="shared" si="1"/>
-        <v>59.835294117647067</v>
-      </c>
+      <c r="L92" s="7"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
@@ -5775,23 +5509,20 @@
         <v>85.882352941176478</v>
       </c>
       <c r="K93" s="6"/>
-      <c r="L93" s="7">
-        <f t="shared" si="1"/>
-        <v>89.432941176470592</v>
-      </c>
+      <c r="L93" s="7"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -5808,23 +5539,20 @@
         <v>80</v>
       </c>
       <c r="K94" s="6"/>
-      <c r="L94" s="7">
-        <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
+      <c r="L94" s="7"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -5841,23 +5569,20 @@
         <v>17.777777777777779</v>
       </c>
       <c r="K95" s="6"/>
-      <c r="L95" s="7">
-        <f t="shared" si="1"/>
-        <v>24.311111111111114</v>
-      </c>
+      <c r="L95" s="7"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
@@ -5874,23 +5599,20 @@
         <v>58.82352941176471</v>
       </c>
       <c r="K96" s="6"/>
-      <c r="L96" s="7">
-        <f t="shared" si="1"/>
-        <v>66.289411764705889</v>
-      </c>
+      <c r="L96" s="7"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
@@ -5907,23 +5629,20 @@
         <v>60</v>
       </c>
       <c r="K97" s="6"/>
-      <c r="L97" s="7">
-        <f t="shared" si="1"/>
-        <v>57.24</v>
-      </c>
+      <c r="L97" s="7"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -5940,23 +5659,20 @@
         <v>29.411764705882355</v>
       </c>
       <c r="K98" s="6"/>
-      <c r="L98" s="7">
-        <f t="shared" si="1"/>
-        <v>50.124705882352941</v>
-      </c>
+      <c r="L98" s="7"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -5973,23 +5689,20 @@
         <v>38.888888888888893</v>
       </c>
       <c r="K99" s="6"/>
-      <c r="L99" s="7">
-        <f t="shared" si="1"/>
-        <v>38.515555555555558</v>
-      </c>
+      <c r="L99" s="7"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -6006,23 +5719,20 @@
         <v>71.764705882352942</v>
       </c>
       <c r="K100" s="6"/>
-      <c r="L100" s="7">
-        <f t="shared" si="1"/>
-        <v>81.265882352941176</v>
-      </c>
+      <c r="L100" s="7"/>
     </row>
     <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -6039,23 +5749,20 @@
         <v>97.64705882352942</v>
       </c>
       <c r="K101" s="6"/>
-      <c r="L101" s="7">
-        <f t="shared" si="1"/>
-        <v>94.058823529411768</v>
-      </c>
+      <c r="L101" s="7"/>
     </row>
     <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -6072,23 +5779,20 @@
         <v>15.555555555555557</v>
       </c>
       <c r="K102" s="6"/>
-      <c r="L102" s="7">
-        <f t="shared" si="1"/>
-        <v>32.862222222222222</v>
-      </c>
+      <c r="L102" s="7"/>
     </row>
     <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -6105,23 +5809,20 @@
         <v>38.82352941176471</v>
       </c>
       <c r="K103" s="6"/>
-      <c r="L103" s="7">
-        <f t="shared" si="1"/>
-        <v>44.729411764705887</v>
-      </c>
+      <c r="L103" s="7"/>
     </row>
     <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -6138,23 +5839,20 @@
         <v>22.352941176470591</v>
       </c>
       <c r="K104" s="6"/>
-      <c r="L104" s="7">
-        <f t="shared" si="1"/>
-        <v>24.301176470588238</v>
-      </c>
+      <c r="L104" s="7"/>
     </row>
     <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -6171,23 +5869,20 @@
         <v>100</v>
       </c>
       <c r="K105" s="6"/>
-      <c r="L105" s="7">
-        <f t="shared" si="1"/>
-        <v>97.12</v>
-      </c>
+      <c r="L105" s="7"/>
     </row>
     <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -6204,23 +5899,20 @@
         <v>77.64705882352942</v>
       </c>
       <c r="K106" s="6"/>
-      <c r="L106" s="7">
-        <f t="shared" si="1"/>
-        <v>84.498823529411766</v>
-      </c>
+      <c r="L106" s="7"/>
     </row>
     <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -6237,23 +5929,20 @@
         <v>58.82352941176471</v>
       </c>
       <c r="K107" s="6"/>
-      <c r="L107" s="7">
-        <f t="shared" si="1"/>
-        <v>75.769411764705893</v>
-      </c>
+      <c r="L107" s="7"/>
     </row>
     <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -6270,23 +5959,20 @@
         <v>82.352941176470594</v>
       </c>
       <c r="K108" s="6"/>
-      <c r="L108" s="7">
-        <f t="shared" si="1"/>
-        <v>71.90117647058824</v>
-      </c>
+      <c r="L108" s="7"/>
     </row>
     <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -6303,23 +5989,20 @@
         <v>55.294117647058826</v>
       </c>
       <c r="K109" s="6"/>
-      <c r="L109" s="7">
-        <f t="shared" si="1"/>
-        <v>63.477647058823536</v>
-      </c>
+      <c r="L109" s="7"/>
     </row>
     <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -6336,23 +6019,20 @@
         <v>74.117647058823536</v>
       </c>
       <c r="K110" s="6"/>
-      <c r="L110" s="7">
-        <f t="shared" si="1"/>
-        <v>73.767058823529425</v>
-      </c>
+      <c r="L110" s="7"/>
     </row>
     <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -6369,23 +6049,20 @@
         <v>54.44444444444445</v>
       </c>
       <c r="K111" s="6"/>
-      <c r="L111" s="7">
-        <f t="shared" si="1"/>
-        <v>37.897777777777783</v>
-      </c>
+      <c r="L111" s="7"/>
     </row>
     <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -6402,23 +6079,20 @@
         <v>58.82352941176471</v>
       </c>
       <c r="K112" s="6"/>
-      <c r="L112" s="7">
-        <f t="shared" si="1"/>
-        <v>71.969411764705882</v>
-      </c>
+      <c r="L112" s="7"/>
     </row>
     <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -6435,23 +6109,20 @@
         <v>54.117647058823529</v>
       </c>
       <c r="K113" s="6"/>
-      <c r="L113" s="7">
-        <f t="shared" si="1"/>
-        <v>71.007058823529405</v>
-      </c>
+      <c r="L113" s="7"/>
     </row>
     <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -6468,23 +6139,20 @@
         <v>15.294117647058824</v>
       </c>
       <c r="K114" s="6"/>
-      <c r="L114" s="7">
-        <f t="shared" si="1"/>
-        <v>23.71764705882353</v>
-      </c>
+      <c r="L114" s="7"/>
     </row>
     <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -6501,23 +6169,20 @@
         <v>58.82352941176471</v>
       </c>
       <c r="K115" s="6"/>
-      <c r="L115" s="7">
-        <f t="shared" si="1"/>
-        <v>74.609411764705897</v>
-      </c>
+      <c r="L115" s="7"/>
     </row>
     <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -6534,23 +6199,20 @@
         <v>100</v>
       </c>
       <c r="K116" s="6"/>
-      <c r="L116" s="7">
-        <f t="shared" si="1"/>
-        <v>98.68</v>
-      </c>
+      <c r="L116" s="7"/>
     </row>
     <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -6567,23 +6229,20 @@
         <v>100</v>
       </c>
       <c r="K117" s="6"/>
-      <c r="L117" s="7">
-        <f t="shared" si="1"/>
-        <v>97.080000000000013</v>
-      </c>
+      <c r="L117" s="7"/>
     </row>
     <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
@@ -6600,23 +6259,20 @@
         <v>98.82352941176471</v>
       </c>
       <c r="K118" s="6"/>
-      <c r="L118" s="7">
-        <f t="shared" si="1"/>
-        <v>98.249411764705883</v>
-      </c>
+      <c r="L118" s="7"/>
     </row>
     <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
@@ -6633,23 +6289,20 @@
         <v>100</v>
       </c>
       <c r="K119" s="6"/>
-      <c r="L119" s="7">
-        <f t="shared" si="1"/>
-        <v>95.64</v>
-      </c>
+      <c r="L119" s="7"/>
     </row>
     <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
@@ -6666,23 +6319,20 @@
         <v>52.941176470588239</v>
       </c>
       <c r="K120" s="6"/>
-      <c r="L120" s="7">
-        <f t="shared" si="1"/>
-        <v>66.416470588235299</v>
-      </c>
+      <c r="L120" s="7"/>
     </row>
     <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -6699,23 +6349,20 @@
         <v>58.82352941176471</v>
       </c>
       <c r="K121" s="6"/>
-      <c r="L121" s="7">
-        <f t="shared" si="1"/>
-        <v>51.969411764705882</v>
-      </c>
+      <c r="L121" s="7"/>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -6732,23 +6379,20 @@
         <v>94.117647058823536</v>
       </c>
       <c r="K122" s="6"/>
-      <c r="L122" s="7">
-        <f t="shared" si="1"/>
-        <v>90.807058823529417</v>
-      </c>
+      <c r="L122" s="7"/>
     </row>
     <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -6765,23 +6409,20 @@
         <v>28.235294117647058</v>
       </c>
       <c r="K123" s="6"/>
-      <c r="L123" s="7">
-        <f t="shared" si="1"/>
-        <v>40.894117647058827</v>
-      </c>
+      <c r="L123" s="7"/>
     </row>
     <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -6798,23 +6439,20 @@
         <v>76.666666666666671</v>
       </c>
       <c r="K124" s="6"/>
-      <c r="L124" s="7">
-        <f t="shared" si="1"/>
-        <v>50.186666666666667</v>
-      </c>
+      <c r="L124" s="7"/>
     </row>
     <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -6831,23 +6469,20 @@
         <v>36.470588235294116</v>
       </c>
       <c r="K125" s="6"/>
-      <c r="L125" s="7">
-        <f t="shared" si="1"/>
-        <v>63.308235294117651</v>
-      </c>
+      <c r="L125" s="7"/>
     </row>
     <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -6864,23 +6499,20 @@
         <v>81.17647058823529</v>
       </c>
       <c r="K126" s="6"/>
-      <c r="L126" s="7">
-        <f t="shared" si="1"/>
-        <v>82.150588235294123</v>
-      </c>
+      <c r="L126" s="7"/>
     </row>
     <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -6897,23 +6529,20 @@
         <v>67.058823529411768</v>
       </c>
       <c r="K127" s="6"/>
-      <c r="L127" s="7">
-        <f t="shared" si="1"/>
-        <v>66.82352941176471</v>
-      </c>
+      <c r="L127" s="7"/>
     </row>
     <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -6930,23 +6559,20 @@
         <v>71.111111111111114</v>
       </c>
       <c r="K128" s="6"/>
-      <c r="L128" s="7">
-        <f t="shared" si="1"/>
-        <v>55.444444444444443</v>
-      </c>
+      <c r="L128" s="7"/>
     </row>
     <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -6963,23 +6589,20 @@
         <v>55.294117647058826</v>
       </c>
       <c r="K129" s="6"/>
-      <c r="L129" s="7">
-        <f t="shared" si="1"/>
-        <v>51.637647058823532</v>
-      </c>
+      <c r="L129" s="7"/>
     </row>
     <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -6996,23 +6619,20 @@
         <v>55.294117647058826</v>
       </c>
       <c r="K130" s="6"/>
-      <c r="L130" s="7">
-        <f t="shared" si="1"/>
-        <v>63.437647058823529</v>
-      </c>
+      <c r="L130" s="7"/>
     </row>
     <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -7029,23 +6649,20 @@
         <v>30</v>
       </c>
       <c r="K131" s="6"/>
-      <c r="L131" s="7">
-        <f t="shared" ref="L131:L146" si="2">G131 * 0.2 + H131 * 0.2 + I131 * 0.2 + J131 * 0.4</f>
-        <v>35.400000000000006</v>
-      </c>
+      <c r="L131" s="7"/>
     </row>
     <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -7062,23 +6679,20 @@
         <v>76.470588235294116</v>
       </c>
       <c r="K132" s="6"/>
-      <c r="L132" s="7">
-        <f t="shared" si="2"/>
-        <v>76.468235294117648</v>
-      </c>
+      <c r="L132" s="7"/>
     </row>
     <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -7095,23 +6709,20 @@
         <v>42.352941176470587</v>
       </c>
       <c r="K133" s="6"/>
-      <c r="L133" s="7">
-        <f t="shared" si="2"/>
-        <v>51.861176470588234</v>
-      </c>
+      <c r="L133" s="7"/>
     </row>
     <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
@@ -7128,23 +6739,20 @@
         <v>67.777777777777786</v>
       </c>
       <c r="K134" s="6"/>
-      <c r="L134" s="7">
-        <f t="shared" si="2"/>
-        <v>51.551111111111119</v>
-      </c>
+      <c r="L134" s="7"/>
     </row>
     <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -7161,23 +6769,20 @@
         <v>28.888888888888889</v>
       </c>
       <c r="K135" s="6"/>
-      <c r="L135" s="7">
-        <f t="shared" si="2"/>
-        <v>42.035555555555561</v>
-      </c>
+      <c r="L135" s="7"/>
     </row>
     <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
@@ -7194,23 +6799,20 @@
         <v>15.294117647058824</v>
       </c>
       <c r="K136" s="6"/>
-      <c r="L136" s="7">
-        <f t="shared" si="2"/>
-        <v>21.437647058823529</v>
-      </c>
+      <c r="L136" s="7"/>
     </row>
     <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -7227,23 +6829,20 @@
         <v>22.352941176470591</v>
       </c>
       <c r="K137" s="6"/>
-      <c r="L137" s="7">
-        <f t="shared" si="2"/>
-        <v>23.261176470588239</v>
-      </c>
+      <c r="L137" s="7"/>
     </row>
     <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
@@ -7260,23 +6859,20 @@
         <v>23.333333333333336</v>
       </c>
       <c r="K138" s="6"/>
-      <c r="L138" s="7">
-        <f t="shared" si="2"/>
-        <v>38.293333333333337</v>
-      </c>
+      <c r="L138" s="7"/>
     </row>
     <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -7293,23 +6889,20 @@
         <v>18.823529411764707</v>
       </c>
       <c r="K139" s="6"/>
-      <c r="L139" s="7">
-        <f t="shared" si="2"/>
-        <v>21.609411764705882</v>
-      </c>
+      <c r="L139" s="7"/>
     </row>
     <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -7324,23 +6917,20 @@
       </c>
       <c r="J140" s="6"/>
       <c r="K140" s="6"/>
-      <c r="L140" s="7">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="L140" s="7"/>
     </row>
     <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -7357,23 +6947,20 @@
         <v>54.44444444444445</v>
       </c>
       <c r="K141" s="6"/>
-      <c r="L141" s="7">
-        <f t="shared" si="2"/>
-        <v>40.937777777777782</v>
-      </c>
+      <c r="L141" s="7"/>
     </row>
     <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -7390,23 +6977,20 @@
         <v>21.111111111111111</v>
       </c>
       <c r="K142" s="6"/>
-      <c r="L142" s="7">
-        <f t="shared" si="2"/>
-        <v>18.644444444444446</v>
-      </c>
+      <c r="L142" s="7"/>
     </row>
     <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -7423,23 +7007,20 @@
         <v>58.888888888888893</v>
       </c>
       <c r="K143" s="6"/>
-      <c r="L143" s="7">
-        <f t="shared" si="2"/>
-        <v>46.555555555555557</v>
-      </c>
+      <c r="L143" s="7"/>
     </row>
     <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -7456,23 +7037,20 @@
         <v>84.705882352941174</v>
       </c>
       <c r="K144" s="6"/>
-      <c r="L144" s="7">
-        <f t="shared" si="2"/>
-        <v>86.362352941176482</v>
-      </c>
+      <c r="L144" s="7"/>
     </row>
     <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
@@ -7489,23 +7067,20 @@
         <v>41.176470588235297</v>
       </c>
       <c r="K145" s="6"/>
-      <c r="L145" s="7">
-        <f t="shared" si="2"/>
-        <v>61.590588235294121</v>
-      </c>
+      <c r="L145" s="7"/>
     </row>
     <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
@@ -7522,32 +7097,14 @@
         <v>10.588235294117647</v>
       </c>
       <c r="K146" s="6"/>
-      <c r="L146" s="7">
-        <f>G146 * 0.2 + H146 * 0.2 + I146 * 0.2 + J146 * 0.4</f>
-        <v>28.075294117647061</v>
-      </c>
+      <c r="L146" s="7"/>
     </row>
     <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G147" s="1">
-        <f>AVERAGE(G2:G146)</f>
-        <v>71.131034482758622</v>
-      </c>
-      <c r="H147" s="1">
-        <f t="shared" ref="H147:J147" si="3">AVERAGE(H2:H146)</f>
-        <v>57.434482758620689</v>
-      </c>
-      <c r="I147" s="1">
-        <f t="shared" si="3"/>
-        <v>56.663448275862073</v>
-      </c>
-      <c r="J147" s="1">
-        <f t="shared" si="3"/>
-        <v>63.980680507497091</v>
-      </c>
-      <c r="L147" s="7">
-        <f>AVERAGE(L2:L146)</f>
-        <v>61.049579445571325</v>
-      </c>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="7"/>
+      <c r="L147" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/docs/data/presentation/MAT111.xlsx
+++ b/docs/data/presentation/MAT111.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\erenimo\projects\ses\docs\data\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1748A35-338E-4F95-AD76-2D068ED46146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E91FA42-CC87-4DB0-8DB9-254882BEC48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -248,12 +248,6 @@
     <t>Midterm II(%20)_0833AB</t>
   </si>
   <si>
-    <t>Homework(%20)_0833AB</t>
-  </si>
-  <si>
-    <t>Final(%40)_0833AB</t>
-  </si>
-  <si>
     <t>261401021</t>
   </si>
   <si>
@@ -1377,6 +1371,12 @@
   </si>
   <si>
     <t>studentsurname145</t>
+  </si>
+  <si>
+    <t>Assignment(%20)_0833AB</t>
+  </si>
+  <si>
+    <t>Final Exam(%40)_0833AB</t>
   </si>
 </sst>
 </file>
@@ -2678,10 +2678,10 @@
         <v>70</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>71</v>
+        <v>446</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>72</v>
+        <v>447</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>5</v>
@@ -3366,13 +3366,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -3394,13 +3394,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -3422,13 +3422,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -3452,13 +3452,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -3482,13 +3482,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -3512,13 +3512,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -3542,13 +3542,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -3572,13 +3572,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -3602,13 +3602,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -3632,13 +3632,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -3662,13 +3662,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -3692,13 +3692,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -3722,13 +3722,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -3752,13 +3752,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -3782,13 +3782,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -3812,13 +3812,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -3842,13 +3842,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -3872,13 +3872,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -3902,13 +3902,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -3932,13 +3932,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -3962,13 +3962,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -3992,13 +3992,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -4022,13 +4022,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -4052,13 +4052,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -4082,13 +4082,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -4112,13 +4112,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -4142,13 +4142,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -4172,13 +4172,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -4202,13 +4202,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -4232,13 +4232,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -4262,13 +4262,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -4292,13 +4292,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
@@ -4322,13 +4322,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -4352,13 +4352,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -4382,13 +4382,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -4412,13 +4412,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -4440,13 +4440,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
@@ -4470,13 +4470,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
@@ -4500,13 +4500,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -4530,13 +4530,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -4560,13 +4560,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
@@ -4590,13 +4590,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -4620,13 +4620,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
@@ -4650,13 +4650,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
@@ -4680,13 +4680,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
@@ -4710,13 +4710,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
@@ -4740,13 +4740,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
@@ -4770,13 +4770,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -4800,13 +4800,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
@@ -4830,13 +4830,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -4860,13 +4860,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
@@ -4890,13 +4890,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
@@ -4920,13 +4920,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
@@ -4950,13 +4950,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -4980,13 +4980,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -5010,13 +5010,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
@@ -5040,13 +5040,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -5070,13 +5070,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -5098,13 +5098,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -5128,13 +5128,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -5158,13 +5158,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -5188,13 +5188,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -5218,13 +5218,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -5248,13 +5248,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -5278,13 +5278,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
@@ -5308,13 +5308,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
@@ -5338,13 +5338,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -5368,13 +5368,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -5398,13 +5398,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -5428,13 +5428,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
@@ -5456,13 +5456,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
@@ -5486,13 +5486,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
@@ -5516,13 +5516,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -5546,13 +5546,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -5576,13 +5576,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
@@ -5606,13 +5606,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
@@ -5636,13 +5636,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -5666,13 +5666,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -5696,13 +5696,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -5726,13 +5726,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -5756,13 +5756,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -5786,13 +5786,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -5816,13 +5816,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -5846,13 +5846,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -5876,13 +5876,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -5906,13 +5906,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -5936,13 +5936,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -5966,13 +5966,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -5996,13 +5996,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -6026,13 +6026,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -6056,13 +6056,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -6086,13 +6086,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -6116,13 +6116,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -6146,13 +6146,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -6176,13 +6176,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -6206,13 +6206,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -6236,13 +6236,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
@@ -6266,13 +6266,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
@@ -6296,13 +6296,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
@@ -6326,13 +6326,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -6356,13 +6356,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -6386,13 +6386,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -6416,13 +6416,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -6446,13 +6446,13 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -6476,13 +6476,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -6506,13 +6506,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -6536,13 +6536,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -6566,13 +6566,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -6596,13 +6596,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -6626,13 +6626,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -6656,13 +6656,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -6686,13 +6686,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -6716,13 +6716,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
@@ -6746,13 +6746,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -6776,13 +6776,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
@@ -6806,13 +6806,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -6836,13 +6836,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
@@ -6866,13 +6866,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -6896,13 +6896,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -6924,13 +6924,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -6954,13 +6954,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -6984,13 +6984,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -7014,13 +7014,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -7044,13 +7044,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
@@ -7074,13 +7074,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
